--- a/event_registration_forms/030_public_speaking_tournament_entry_form--event_registration_forms.xlsx
+++ b/event_registration_forms/030_public_speaking_tournament_entry_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'type_1',_'value':_'type-1'}</t>
+          <t>type_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Type 1', 'value': 'type-1'}</t>
+          <t>Type 1</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'type_2',_'value':_'type-2'}</t>
+          <t>type_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Type 2', 'value': 'type-2'}</t>
+          <t>Type 2</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'type_3',_'value':_'type-3'}</t>
+          <t>type_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Type 3', 'value': 'type-3'}</t>
+          <t>Type 3</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'type_1',_'value':_'type-1'}</t>
+          <t>type_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'Type 1', 'value': 'type-1'}</t>
+          <t>Type 1</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'type_2',_'value':_'type-2'}</t>
+          <t>type_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'Type 2', 'value': 'type-2'}</t>
+          <t>Type 2</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_'type_3',_'value':_'type-3'}</t>
+          <t>type_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 'Type 3', 'value': 'type-3'}</t>
+          <t>Type 3</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_30,_'label':_'status_1',_'value':_'status-1'}</t>
+          <t>status_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 30, 'label': 'Status 1', 'value': 'status-1'}</t>
+          <t>Status 1</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_31,_'label':_'status_2',_'value':_'status-2'}</t>
+          <t>status_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 31, 'label': 'Status 2', 'value': 'status-2'}</t>
+          <t>Status 2</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_32,_'label':_'status_3',_'value':_'status-3'}</t>
+          <t>status_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 32, 'label': 'Status 3', 'value': 'status-3'}</t>
+          <t>Status 3</t>
         </is>
       </c>
     </row>
